--- a/stories/arbres/ATOM-REL.CON.002-04.xlsx
+++ b/stories/arbres/ATOM-REL.CON.002-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Hortense est dans la cour. La maîtresse est près du préau. Hortense joue avec le cerceau. Achille arrive vite. Achille bouscule Hortense. Hortense sent ses pieds bouger. Hortense dit : stop. Elle fait un pas. Elle doit s'éloigner. S'éloigner, c'est aller vers la maîtresse. Hortense marche vers la maîtresse. Elle dit : Achille m'a bousculée. La maîtresse l'écoute. Plus tard, près des plots, Achille bouscule encore. Hortense dit encore : stop. Elle s'éloigne. Elle va vers la maîtresse. La maîtresse dit : tu as dit stop. Tu t'es éloignée. Tu es venue me voir. Le soir, papa vient. Hortense raconte à papa. Papa dit : tu as bien fait. On dit stop. On s'éloigne. On va vers la maîtresse. Hortense serre la main de papa.</t>
+          <t>Hortense est dans la cour. La maîtresse est près du préau. Hortense joue avec le cerceau. Achille arrive vite. Achille bouscule Hortense. Hortense sent ses pieds bouger. Stop. Elle fait un pas. Elle doit s'éloigner. S'éloigner, c'est aller vers la maîtresse. Hortense marche vers la maîtresse. Achille m'a bousculée. La maîtresse l'écoute. Plus tard, près des plots, Achille bouscule encore. Hortense dit encore : stop. Elle s'éloigne. Elle va vers la maîtresse. Tu as dit stop. Tu t'es éloignée. Tu es venue me voir. Le soir, papa vient. Hortense raconte à papa. Tu as bien fait. On dit stop. On s'éloigne. On va vers la maîtresse. Hortense serre la main de papa.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,19 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Hortense est dans la cour. La maîtresse est près du préau. Hortense joue avec le cerceau. Achille arrive vite. Achille bouscule Hortense. Hortense sent ses pieds bouger.
+enfant-f|Stop. Elle fait un pas. Elle doit s'éloigner. S'éloigner, c'est aller vers la maîtresse.
+narrateur|Hortense marche vers la maîtresse.
+narrateur|Achille m'a bousculée.
+narrateur|La maîtresse l'écoute. Plus tard, près des plots, Achille bouscule encore. Hortense dit encore : stop. Elle s'éloigne. Elle va vers la maîtresse.
+maitresse|Tu as dit stop. Tu t'es éloignée. Tu es venue me voir.
+narrateur|Le soir, papa vient. Hortense raconte à papa.
+papa|Tu as bien fait. On dit stop. On s'éloigne. On va vers la maîtresse.
+narrateur|Hortense serre la main de papa.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1494,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Un camarade bouscule Hortense. Que fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1667,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Hortense a dit stop. Elle a su s'éloigner. Elle a rejoint la maîtresse. Papa a écouté.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1830,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Hortense range son manteau. Papa marche à côté.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1997,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2037,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.CON.002-04.xlsx
+++ b/stories/arbres/ATOM-REL.CON.002-04.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1318,6 +1323,7 @@
 narrateur|Hortense serre la main de papa.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1501,6 +1507,7 @@
           <t>narrateur|Un camarade bouscule Hortense. Que fait-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1672,6 +1679,7 @@
           <t>narrateur|Hortense a dit stop. Elle a su s'éloigner. Elle a rejoint la maîtresse. Papa a écouté.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1835,6 +1843,7 @@
           <t>narrateur|Hortense range son manteau. Papa marche à côté.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2002,6 +2011,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2020,7 +2030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2044,6 +2054,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2058,7 +2082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2245,6 +2269,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-REL.CON.002-04.xlsx
+++ b/stories/arbres/ATOM-REL.CON.002-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Hortense dit stop à la cour</t>
+          <t>Victorina dit stop à la cour</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Victorina joue au cerceau. Chouchou passe trop près, deux fois. Elle dit stop, s'éloigne, rejoint la maîtresse.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Hortense est dans la cour. La maîtresse est près du préau. Hortense joue avec le cerceau. Achille arrive vite. Achille bouscule Hortense. Hortense sent ses pieds bouger. Stop. Elle fait un pas. Elle doit s'éloigner. S'éloigner, c'est aller vers la maîtresse. Hortense marche vers la maîtresse. Achille m'a bousculée. La maîtresse l'écoute. Plus tard, près des plots, Achille bouscule encore. Hortense dit encore : stop. Elle s'éloigne. Elle va vers la maîtresse. Tu as dit stop. Tu t'es éloignée. Tu es venue me voir. Le soir, papa vient. Hortense raconte à papa. Tu as bien fait. On dit stop. On s'éloigne. On va vers la maîtresse. Hortense serre la main de papa.</t>
+          <t>Des feuilles mouillées collent aux chaussures. Elles font un bruit doux, tout plat. Une feuille jaune reste sous le talon. Derrière le mur, le pain du fournil sent chaud. Une bouffée passe au-dessus du grillage. Papa pose le cartable sous le préau. Tu as senti le pain, Victorina ? Oui, papa. Il sent le chaud. Le fournil est juste derrière. Je reviens ce soir. D'accord. La maîtresse est près du préau. En ce moment, Victorina est dans la cour. Elle joue avec le cerceau. Le cerceau roule, puis s'arrête. Il roule bien. Victorina le relance. Une feuille colle au cerceau. Elle la retire, tout doux. Chouchou arrive très vite. Chouchou passe trop près. Victorina sent ses pieds bouger. Son cœur tape. Stop. Victorina fait un pas. Elle peut s'éloigner. S'éloigner, c'est aller vers la maîtresse. Victorina marche vers le préau. Chouchou est passé trop près. La maîtresse l'écoute. Victorina reste près d'elle. Plus tard, près des plots oranges, Chouchou arrive encore. Il passe trop près encore. Victorina se souvient. Stop. Elle s'éloigne. Elle va vers la maîtresse. Je suis venue. La maîtresse l'écoute encore. Victorina reste près d'elle. Elle pose une main sur un plot orange. Le plot est lisse et un peu tiède. Je reste ici. Victorina souffle. Son cœur tape moins vite. Le soir, papa revient. Les feuilles collent encore aux chaussures. Victorina secoue une feuille du talon. La feuille tombe, toute plate. Tu as joué au cerceau ? Oui. Chouchou est passé trop près. Deux fois. J'ai dit stop. Je suis allée vers la maîtresse. Bravo, Victorina. Tu as dit stop. Tu t'es éloignée. Tu es allée vers la maîtresse. C'est du bon travail. Même près des plots ? Oui. Stop encore. Même leçon, autre endroit. Oui, papa. Victorina serre la main de papa. Le pain du fournil sent encore, tout doux.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,15 +1324,74 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Hortense est dans la cour. La maîtresse est près du préau. Hortense joue avec le cerceau. Achille arrive vite. Achille bouscule Hortense. Hortense sent ses pieds bouger.
-enfant-f|Stop. Elle fait un pas. Elle doit s'éloigner. S'éloigner, c'est aller vers la maîtresse.
-narrateur|Hortense marche vers la maîtresse.
-narrateur|Achille m'a bousculée.
-narrateur|La maîtresse l'écoute. Plus tard, près des plots, Achille bouscule encore. Hortense dit encore : stop. Elle s'éloigne. Elle va vers la maîtresse.
-maitresse|Tu as dit stop. Tu t'es éloignée. Tu es venue me voir.
-narrateur|Le soir, papa vient. Hortense raconte à papa.
-papa|Tu as bien fait. On dit stop. On s'éloigne. On va vers la maîtresse.
-narrateur|Hortense serre la main de papa.</t>
+          <t>narrateur|Des feuilles mouillées collent aux chaussures.
+narrateur|Elles font un bruit doux, tout plat.
+narrateur|Une feuille jaune reste sous le talon.
+narrateur|Derrière le mur, le pain du fournil sent chaud.
+narrateur|Une bouffée passe au-dessus du grillage.
+narrateur|Papa pose le cartable sous le préau.
+papa|Tu as senti le pain, Victorina ?
+enfant-f|Oui, papa.
+enfant-f|Il sent le chaud.
+papa|Le fournil est juste derrière.
+papa|Je reviens ce soir.
+enfant-f|D'accord.
+narrateur|La maîtresse est près du préau.
+narrateur|En ce moment, Victorina est dans la cour.
+narrateur|Elle joue avec le cerceau.
+narrateur|Le cerceau roule, puis s'arrête.
+enfant-f|Il roule bien.
+narrateur|Victorina le relance.
+narrateur|Une feuille colle au cerceau.
+narrateur|Elle la retire, tout doux.
+narrateur|Chouchou arrive très vite.
+narrateur|Chouchou passe trop près.
+narrateur|Victorina sent ses pieds bouger.
+narrateur|Son cœur tape.
+enfant-f|Stop.
+narrateur|Victorina fait un pas.
+narrateur|Elle peut s'éloigner.
+narrateur|S'éloigner, c'est aller vers la maîtresse.
+narrateur|Victorina marche vers le préau.
+enfant-f|Chouchou est passé trop près.
+narrateur|La maîtresse l'écoute.
+narrateur|Victorina reste près d'elle.
+narrateur|Plus tard, près des plots oranges, Chouchou arrive encore.
+narrateur|Il passe trop près encore.
+narrateur|Victorina se souvient.
+enfant-f|Stop.
+narrateur|Elle s'éloigne.
+narrateur|Elle va vers la maîtresse.
+enfant-f|Je suis venue.
+narrateur|La maîtresse l'écoute encore.
+narrateur|Victorina reste près d'elle.
+narrateur|Elle pose une main sur un plot orange.
+narrateur|Le plot est lisse et un peu tiède.
+enfant-f|Je reste ici.
+narrateur|Victorina souffle.
+narrateur|Son cœur tape moins vite.
+narrateur|Le soir, papa revient.
+narrateur|Les feuilles collent encore aux chaussures.
+narrateur|Victorina secoue une feuille du talon.
+narrateur|La feuille tombe, toute plate.
+papa|Tu as joué au cerceau ?
+enfant-f|Oui.
+enfant-f|Chouchou est passé trop près.
+enfant-f|Deux fois.
+enfant-f|J'ai dit stop.
+enfant-f|Je suis allée vers la maîtresse.
+papa|Bravo, Victorina.
+papa|Tu as dit stop.
+papa|Tu t'es éloignée.
+papa|Tu es allée vers la maîtresse.
+papa|C'est du bon travail.
+papa|Même près des plots ?
+enfant-f|Oui.
+enfant-f|Stop encore.
+papa|Même leçon, autre endroit.
+enfant-f|Oui, papa.
+narrateur|Victorina serre la main de papa.
+narrateur|Le pain du fournil sent encore, tout doux.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1348,7 +1419,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Un camarade bouscule Hortense. Que fait-elle ?</t>
+          <t>Un camarade bouscule Victorina. Que fait-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1504,7 +1575,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Un camarade bouscule Hortense. Que fait-elle ?</t>
+          <t>narrateur|Un camarade bouscule Victorina.
+narrateur|Que fait-elle ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1532,7 +1604,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Hortense a dit stop. Elle a su s'éloigner. Elle a rejoint la maîtresse. Papa a écouté.</t>
+          <t>Victorina a dit stop. Elle s'est éloignée. Elle a rejoint la maîtresse. Bravo. Tu as su deux fois. Stop, puis la maîtresse. Oui. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1676,7 +1748,14 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Hortense a dit stop. Elle a su s'éloigner. Elle a rejoint la maîtresse. Papa a écouté.</t>
+          <t>narrateur|Victorina a dit stop.
+narrateur|Elle s'est éloignée.
+narrateur|Elle a rejoint la maîtresse.
+papa|Bravo.
+papa|Tu as su deux fois.
+enfant-f|Stop, puis la maîtresse.
+papa|Oui.
+papa|Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1704,7 +1783,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Hortense range son manteau. Papa marche à côté.</t>
+          <t>Victorina range son manteau. Une feuille mouillée reste sous la chaussure. On marche à côté ? Oui, papa. Tu tiens ma main ? Oui. Tu sens encore le pain ? Un peu. Les plots oranges restent dans la cour. Le cerceau ne roule plus. On sent encore le fournil ? Un tout petit peu. Une feuille sèche sur le chemin.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1840,7 +1919,19 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Hortense range son manteau. Papa marche à côté.</t>
+          <t>narrateur|Victorina range son manteau.
+narrateur|Une feuille mouillée reste sous la chaussure.
+papa|On marche à côté ?
+enfant-f|Oui, papa.
+papa|Tu tiens ma main ?
+enfant-f|Oui.
+papa|Tu sens encore le pain ?
+enfant-f|Un peu.
+narrateur|Les plots oranges restent dans la cour.
+narrateur|Le cerceau ne roule plus.
+papa|On sent encore le fournil ?
+enfant-f|Un tout petit peu.
+narrateur|Une feuille sèche sur le chemin.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1868,7 +1959,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai dit stop. Je suis allée vers la maîtresse. Bravo, Victorina. Tu as fait du bon travail. Les feuilles mouillées restent au sol. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2008,7 +2099,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai dit stop.
+enfant-f|Je suis allée vers la maîtresse.
+papa|Bravo, Victorina.
+papa|Tu as fait du bon travail.
+narrateur|Les feuilles mouillées restent au sol.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2030,7 +2126,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2068,6 +2164,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.CON.002-04.xlsx
+++ b/stories/arbres/ATOM-REL.CON.002-04.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Des feuilles mouillées collent aux chaussures. Elles font un bruit doux, tout plat. Une feuille jaune reste sous le talon. Derrière le mur, le pain du fournil sent chaud. Une bouffée passe au-dessus du grillage. Papa pose le cartable sous le préau. Tu as senti le pain, Victorina ? Oui, papa. Il sent le chaud. Le fournil est juste derrière. Je reviens ce soir. D'accord. La maîtresse est près du préau. En ce moment, Victorina est dans la cour. Elle joue avec le cerceau. Le cerceau roule, puis s'arrête. Il roule bien. Victorina le relance. Une feuille colle au cerceau. Elle la retire, tout doux. Chouchou arrive très vite. Chouchou passe trop près. Victorina sent ses pieds bouger. Son cœur tape. Stop. Victorina fait un pas. Elle peut s'éloigner. S'éloigner, c'est aller vers la maîtresse. Victorina marche vers le préau. Chouchou est passé trop près. La maîtresse l'écoute. Victorina reste près d'elle. Plus tard, près des plots oranges, Chouchou arrive encore. Il passe trop près encore. Victorina se souvient. Stop. Elle s'éloigne. Elle va vers la maîtresse. Je suis venue. La maîtresse l'écoute encore. Victorina reste près d'elle. Elle pose une main sur un plot orange. Le plot est lisse et un peu tiède. Je reste ici. Victorina souffle. Son cœur tape moins vite. Le soir, papa revient. Les feuilles collent encore aux chaussures. Victorina secoue une feuille du talon. La feuille tombe, toute plate. Tu as joué au cerceau ? Oui. Chouchou est passé trop près. Deux fois. J'ai dit stop. Je suis allée vers la maîtresse. Bravo, Victorina. Tu as dit stop. Tu t'es éloignée. Tu es allée vers la maîtresse. C'est du bon travail. Même près des plots ? Oui. Stop encore. Même leçon, autre endroit. Oui, papa. Victorina serre la main de papa. Le pain du fournil sent encore, tout doux.</t>
+          <t>Des feuilles mouillées collent aux chaussures. Elles font un bruit doux, tout plat. Une feuille jaune reste sous le talon. Derrière le mur, le pain du fournil sent chaud. Une bouffée passe au-dessus du grillage. Papa pose le cartable sous le préau. Tu as senti le pain, Victorina ? Oui, papa. Il sent le chaud. Le fournil est juste derrière. Je reviens ce soir. D'accord. La maîtresse est près du préau. En ce moment, Victorina est dans la cour. Elle joue avec le cerceau. Le cerceau roule, puis s'arrête. Il roule bien. Victorina le relance. Une feuille colle au cerceau. Elle la retire, tout doux. Chouchou arrive très vite. Chouchou passe trop près. Victorina sent ses pieds bouger. Son cœur tape. Stop. Victorina fait un pas. Elle peut s'éloigner. S'éloigner, c'est aller vers la maîtresse. Victorina marche vers le préau. Chouchou est passé trop près. La maîtresse l'écoute. Victorina reste près d'elle. Plus tard, près des plots oranges, Chouchou arrive encore. Il passe trop près encore. Victorina se souvient. Stop. Elle s'éloigne. Elle va vers la maîtresse. Je suis venue. La maîtresse l'écoute encore. Victorina reste près d'elle. Elle pose une main sur un plot orange. Le plot est lisse et un peu tiède. Je reste ici. Victorina souffle. Son cœur tape moins vite. Le soir, papa revient. Les feuilles collent encore aux chaussures. Victorina secoue une feuille du talon. La feuille tombe, toute plate. Tu as joué au cerceau ? Oui. Chouchou est passé trop près. Deux fois. J'ai dit stop. Je suis allée vers la maîtresse. Bravo, Victorina. Tu as dit stop. Tu t'es éloignée. Tu es allée vers la maîtresse. Même près des plots ? Oui. Stop encore. Même leçon, autre endroit. Oui, papa. Victorina serre la main de papa. Le pain du fournil sent encore, tout doux.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Hortense est dans la cour. La maîtresse est près du préau. Hortense joue avec le cerceau. Achille arrive vite. Achille bouscule Hortense. Hortense sent ses pieds bouger. Hortense dit : &lt;emphasis level="moderate"&gt;stop&lt;/emphasis&gt;. Elle fait un pas. Elle doit s'éloigner. S'éloigner, c'est aller vers la maîtresse. Hortense marche vers la maîtresse. Elle dit : Achille m'a bousculée. La maîtresse l'écoute. Plus tard, près des plots, Achille bouscule encore. Hortense dit encore : stop. Elle s'éloigne. Elle va vers la maîtresse. La maîtresse dit : tu as dit stop. Tu t'es éloignée. Tu es venue me voir. Le soir, papa vient. Hortense raconte à papa. Papa dit : tu as bien fait. On dit stop. On s'éloigne. On va vers la maîtresse. Hortense serre la main de papa.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Des feuilles mouillées collent aux chaussures. Elles font un bruit doux, tout plat. Une feuille jaune reste sous le talon. Derrière le mur, le pain du fournil sent chaud. Une bouffée passe au-dessus du grillage. Papa pose le cartable sous le préau. Tu as senti le pain, Victorina ? Oui, papa. Il sent le chaud. Le fournil est juste derrière. Je reviens ce soir. D'accord. La maîtresse est près du préau. En ce moment, Victorina est dans la cour. Elle joue avec le cerceau. Le cerceau roule, puis s'arrête. Il roule bien. Victorina le relance. Une feuille colle au cerceau. Elle la retire, tout doux. Chouchou arrive très vite. Chouchou passe trop près. Victorina sent ses pieds bouger. Son cœur tape. Stop. Victorina fait un pas. Elle peut s'éloigner. S'éloigner, c'est aller vers la maîtresse. Victorina marche vers le préau. Chouchou est passé trop près. La maîtresse l'écoute. Victorina reste près d'elle. Plus tard, près des plots oranges, Chouchou arrive encore. Il passe trop près encore. Victorina se souvient. Stop. Elle s'éloigne. Elle va vers la maîtresse. Je suis venue. La maîtresse l'écoute encore. Victorina reste près d'elle. Elle pose une main sur un plot orange. Le plot est lisse et un peu tiède. Je reste ici. Victorina souffle. Son cœur tape moins vite. Le soir, papa revient. Les feuilles collent encore aux chaussures. Victorina secoue une feuille du talon. La feuille tombe, toute plate. Tu as joué au cerceau ? Oui. Chouchou est passé trop près. Deux fois. J'ai dit stop. Je suis allée vers la maîtresse. Bravo, Victorina. Tu as dit stop. Tu t'es éloignée. Tu es allée vers la maîtresse. Même près des plots ? Oui. Stop encore. Même leçon, autre endroit. Oui, papa. Victorina serre la main de papa. Le pain du fournil sent encore, tout doux.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1384,7 +1384,6 @@
 papa|Tu as dit stop.
 papa|Tu t'es éloignée.
 papa|Tu es allée vers la maîtresse.
-papa|C'est du bon travail.
 papa|Même près des plots ?
 enfant-f|Oui.
 enfant-f|Stop encore.
@@ -1394,7 +1393,6 @@
 narrateur|Le pain du fournil sent encore, tout doux.</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1424,7 +1422,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Un camarade bouscule Hortense. Que fait-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Un camarade bouscule Victorina. Que fait-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1579,7 +1577,6 @@
 narrateur|Que fait-elle ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1604,12 +1601,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Victorina a dit stop. Elle s'est éloignée. Elle a rejoint la maîtresse. Bravo. Tu as su deux fois. Stop, puis la maîtresse. Oui. Tu as fait du bon travail.</t>
+          <t>Victorina a dit stop. Elle s'est éloignée. Elle a rejoint la maîtresse. Bravo. Tu as su deux fois. Stop, puis la maîtresse. Oui.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Hortense a dit &lt;emphasis level="moderate"&gt;stop&lt;/emphasis&gt;. Elle a su s'éloigner. Elle a rejoint la maîtresse. Papa a écouté.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorina a dit stop. Elle s'est éloignée. Elle a rejoint la maîtresse. Bravo. Tu as su deux fois. Stop, puis la maîtresse. Oui.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1754,11 +1751,9 @@
 papa|Bravo.
 papa|Tu as su deux fois.
 enfant-f|Stop, puis la maîtresse.
-papa|Oui.
-papa|Tu as fait du bon travail.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+papa|Oui.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1788,7 +1783,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Hortense range son manteau. Papa marche à côté.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorina range son manteau. Une feuille mouillée reste sous la chaussure. On marche à côté ? Oui, papa. Tu tiens ma main ? Oui. Tu sens encore le pain ? Un peu. Les plots oranges restent dans la cour. Le cerceau ne roule plus. On sent encore le fournil ? Un tout petit peu. Une feuille sèche sur le chemin.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1934,7 +1929,6 @@
 narrateur|Une feuille sèche sur le chemin.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1959,12 +1953,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai dit stop. Je suis allée vers la maîtresse. Bravo, Victorina. Tu as fait du bon travail. Les feuilles mouillées restent au sol. L'histoire est finie.</t>
+          <t>J'ai dit stop. Je suis allée vers la maîtresse. Bravo, Victorina. Les feuilles mouillées restent au sol.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai dit stop. Je suis allée vers la maîtresse. Bravo, Victorina. Les feuilles mouillées restent au sol.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2102,12 +2096,9 @@
           <t>enfant-f|J'ai dit stop.
 enfant-f|Je suis allée vers la maîtresse.
 papa|Bravo, Victorina.
-papa|Tu as fait du bon travail.
-narrateur|Les feuilles mouillées restent au sol.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|Les feuilles mouillées restent au sol.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2126,7 +2117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2171,6 +2162,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.CON.002-04.xlsx
+++ b/stories/arbres/ATOM-REL.CON.002-04.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Hortense, Achille, maîtresse, papa</t>
+          <t>Victorina, Chouchou, maîtresse, papa</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.CON.002-04.xlsx
+++ b/stories/arbres/ATOM-REL.CON.002-04.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Victorina dit stop à la cour</t>
+          <t>Le cerceau sous les feuilles</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>cour de l'école</t>
+          <t>cour d'école, feuilles, fournil, plots oranges</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Victorina, Chouchou, maîtresse, papa</t>
+          <t>Victorina, Chouchou, papa</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Victorina joue au cerceau. Chouchou passe trop près, deux fois. Elle dit stop, s'éloigne, rejoint la maîtresse.</t>
+          <t>Victorina veut faire rouler le cerceau jusqu'au mur. Chouchou passe trop près. Elle dit stop, marche vers la maîtresse. Plus tard, près des plots chauds, le cerceau retombe. Elle dit stop encore, va près d'elle. Le pain du fournil reste.</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Des feuilles mouillées collent aux chaussures. Elles font un bruit doux, tout plat. Une feuille jaune reste sous le talon. Derrière le mur, le pain du fournil sent chaud. Une bouffée passe au-dessus du grillage. Papa pose le cartable sous le préau. Tu as senti le pain, Victorina ? Oui, papa. Il sent le chaud. Le fournil est juste derrière. Je reviens ce soir. D'accord. La maîtresse est près du préau. En ce moment, Victorina est dans la cour. Elle joue avec le cerceau. Le cerceau roule, puis s'arrête. Il roule bien. Victorina le relance. Une feuille colle au cerceau. Elle la retire, tout doux. Chouchou arrive très vite. Chouchou passe trop près. Victorina sent ses pieds bouger. Son cœur tape. Stop. Victorina fait un pas. Elle peut s'éloigner. S'éloigner, c'est aller vers la maîtresse. Victorina marche vers le préau. Chouchou est passé trop près. La maîtresse l'écoute. Victorina reste près d'elle. Plus tard, près des plots oranges, Chouchou arrive encore. Il passe trop près encore. Victorina se souvient. Stop. Elle s'éloigne. Elle va vers la maîtresse. Je suis venue. La maîtresse l'écoute encore. Victorina reste près d'elle. Elle pose une main sur un plot orange. Le plot est lisse et un peu tiède. Je reste ici. Victorina souffle. Son cœur tape moins vite. Le soir, papa revient. Les feuilles collent encore aux chaussures. Victorina secoue une feuille du talon. La feuille tombe, toute plate. Tu as joué au cerceau ? Oui. Chouchou est passé trop près. Deux fois. J'ai dit stop. Je suis allée vers la maîtresse. Bravo, Victorina. Tu as dit stop. Tu t'es éloignée. Tu es allée vers la maîtresse. Même près des plots ? Oui. Stop encore. Même leçon, autre endroit. Oui, papa. Victorina serre la main de papa. Le pain du fournil sent encore, tout doux.</t>
+          <t>Le fournil envoie une bouffée de pain chaud. La bouffée passe au-dessus du grillage. Des feuilles jaunes collent aux chaussures. Elles font un bruit doux, tout plat. Une feuille reste sous le talon de Victorina. Le préau sent encore le bois mouillé. Papa pose le cartable près d'un pilier. Tu as senti le pain, Victorina ? Oui, papa. Il sent le chaud. Le fournil est juste derrière. Je reviens ce soir. D'accord. Papa part vers le grillage. La maîtresse est près du préau. En ce moment, Victorina prend le cerceau. Le bois du cerceau est lisse, un peu froid. Je veux le faire rouler jusqu'au mur. Elle pousse le cerceau entre les feuilles. Il roule, puis s'arrête près d'une flaque. Encore. Une feuille colle au bois. Elle la retire, tout doux. Le cerceau repart, plus loin. Chouchou arrive très vite. Chouchou passe trop près du cerceau. Le cerceau penche, puis tombe. Victorina sent ses pieds bouger. Son cœur tape. Stop. Sa voix est claire. Elle fait un pas vers le préau. Ses chaussures froissent les feuilles. Elle marche jusqu'à la maîtresse. Chouchou est passé trop près. La maîtresse l'écoute. Victorina reste près d'elle. Elle pose une main sur le pilier. Le pilier est froid et un peu rugueux. Je reste ici. Le cerceau attend dans les feuilles. Victorina souffle. Son cœur tape moins vite. Plus tard, le soleil a bougé. Les plots oranges sont chauds au milieu. Victorina reprend le cerceau. Je veux passer entre les plots. Le cerceau roule vers l'orange. Il frappe un plot, tout doux. Le plot tremble, puis tient. Encore. Chouchou arrive encore, très vite. Il passe trop près des plots. Le cerceau tombe contre un plot. Le plastique fait un petit bruit creux. Victorina sent encore son cœur. Stop. Elle fait un pas. La maîtresse est près du portail, maintenant. Victorina marche vers elle. L'orange des plots reste derrière. Encore trop près. La maîtresse l'écoute encore. Victorina reste près d'elle. Elle touche un plot, au passage. Le plot est lisse et tiède. Je reste ici. Elle souffle. Le cerceau ne roule plus. Le soir, papa revient. Les feuilles collent encore aux chaussures. Victorina secoue une feuille du talon. La feuille tombe, toute plate. Tu as senti le pain, encore ? Un peu. Le cerceau a roulé. Chouchou est passé trop près. J'ai dit stop. Je suis allée vers la maîtresse. Près du préau ? Oui. Et près des plots ? Stop encore. Bravo, Victorina. Tu es allée près d'elle. Oui, papa. Victorina serre la main de papa. La bouffée de pain revient, tout doux.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Des feuilles mouillées collent aux chaussures. Elles font un bruit doux, tout plat. Une feuille jaune reste sous le talon. Derrière le mur, le pain du fournil sent chaud. Une bouffée passe au-dessus du grillage. Papa pose le cartable sous le préau. Tu as senti le pain, Victorina ? Oui, papa. Il sent le chaud. Le fournil est juste derrière. Je reviens ce soir. D'accord. La maîtresse est près du préau. En ce moment, Victorina est dans la cour. Elle joue avec le cerceau. Le cerceau roule, puis s'arrête. Il roule bien. Victorina le relance. Une feuille colle au cerceau. Elle la retire, tout doux. Chouchou arrive très vite. Chouchou passe trop près. Victorina sent ses pieds bouger. Son cœur tape. Stop. Victorina fait un pas. Elle peut s'éloigner. S'éloigner, c'est aller vers la maîtresse. Victorina marche vers le préau. Chouchou est passé trop près. La maîtresse l'écoute. Victorina reste près d'elle. Plus tard, près des plots oranges, Chouchou arrive encore. Il passe trop près encore. Victorina se souvient. Stop. Elle s'éloigne. Elle va vers la maîtresse. Je suis venue. La maîtresse l'écoute encore. Victorina reste près d'elle. Elle pose une main sur un plot orange. Le plot est lisse et un peu tiède. Je reste ici. Victorina souffle. Son cœur tape moins vite. Le soir, papa revient. Les feuilles collent encore aux chaussures. Victorina secoue une feuille du talon. La feuille tombe, toute plate. Tu as joué au cerceau ? Oui. Chouchou est passé trop près. Deux fois. J'ai dit stop. Je suis allée vers la maîtresse. Bravo, Victorina. Tu as dit stop. Tu t'es éloignée. Tu es allée vers la maîtresse. Même près des plots ? Oui. Stop encore. Même leçon, autre endroit. Oui, papa. Victorina serre la main de papa. Le pain du fournil sent encore, tout doux.</t>
+          <t>Le fournil envoie une bouffée de pain chaud. La bouffée passe au-dessus du grillage. Des feuilles jaunes collent aux chaussures. Elles font un bruit doux, tout plat. Une feuille reste sous le talon de Victorina. Le préau sent encore le bois mouillé. Papa pose le cartable près d'un pilier. Tu as senti le pain, Victorina ? Oui, papa. Il sent le chaud. Le fournil est juste derrière. Je reviens ce soir. D'accord. Papa part vers le grillage. La maîtresse est près du préau. En ce moment, Victorina prend le cerceau. Le bois du cerceau est lisse, un peu froid. Je veux le faire rouler jusqu'au mur. Elle pousse le cerceau entre les feuilles. Il roule, puis s'arrête près d'une flaque. Encore. Une feuille colle au bois. Elle la retire, tout doux. Le cerceau repart, plus loin. Chouchou arrive très vite. Chouchou passe trop près du cerceau. Le cerceau penche, puis tombe. Victorina sent ses pieds bouger. Son cœur tape. Stop. Sa voix est claire. Elle fait un pas vers le préau. Ses chaussures froissent les feuilles. Elle marche jusqu'à la maîtresse. Chouchou est passé trop près. La maîtresse l'écoute. Victorina reste près d'elle. Elle pose une main sur le pilier. Le pilier est froid et un peu rugueux. Je reste ici. Le cerceau attend dans les feuilles. Victorina souffle. Son cœur tape moins vite. Plus tard, le soleil a bougé. Les plots oranges sont chauds au milieu. Victorina reprend le cerceau. Je veux passer entre les plots. Le cerceau roule vers l'orange. Il frappe un plot, tout doux. Le plot tremble, puis tient. Encore. Chouchou arrive encore, très vite. Il passe trop près des plots. Le cerceau tombe contre un plot. Le plastique fait un petit bruit creux. Victorina sent encore son cœur. Stop. Elle fait un pas. La maîtresse est près du portail, maintenant. Victorina marche vers elle. L'orange des plots reste derrière. Encore trop près. La maîtresse l'écoute encore. Victorina reste près d'elle. Elle touche un plot, au passage. Le plot est lisse et tiède. Je reste ici. Elle souffle. Le cerceau ne roule plus. Le soir, papa revient. Les feuilles collent encore aux chaussures. Victorina secoue une feuille du talon. La feuille tombe, toute plate. Tu as senti le pain, encore ? Un peu. Le cerceau a roulé. Chouchou est passé trop près. J'ai dit stop. Je suis allée vers la maîtresse. Près du préau ? Oui. Et près des plots ? Stop encore. Bravo, Victorina. Tu es allée près d'elle. Oui, papa. Victorina serre la main de papa. La bouffée de pain revient, tout doux.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1252,7 +1252,7 @@
         <v>0.96</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1324,73 +1324,94 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Des feuilles mouillées collent aux chaussures.
+          <t>narrateur|Le fournil envoie une bouffée de pain chaud.
+narrateur|La bouffée passe au-dessus du grillage.
+narrateur|Des feuilles jaunes collent aux chaussures.
 narrateur|Elles font un bruit doux, tout plat.
-narrateur|Une feuille jaune reste sous le talon.
-narrateur|Derrière le mur, le pain du fournil sent chaud.
-narrateur|Une bouffée passe au-dessus du grillage.
-narrateur|Papa pose le cartable sous le préau.
+narrateur|Une feuille reste sous le talon de Victorina.
+narrateur|Le préau sent encore le bois mouillé.
+narrateur|Papa pose le cartable près d'un pilier.
 papa|Tu as senti le pain, Victorina ?
 enfant-f|Oui, papa.
 enfant-f|Il sent le chaud.
 papa|Le fournil est juste derrière.
 papa|Je reviens ce soir.
 enfant-f|D'accord.
+narrateur|Papa part vers le grillage.
 narrateur|La maîtresse est près du préau.
-narrateur|En ce moment, Victorina est dans la cour.
-narrateur|Elle joue avec le cerceau.
-narrateur|Le cerceau roule, puis s'arrête.
-enfant-f|Il roule bien.
-narrateur|Victorina le relance.
-narrateur|Une feuille colle au cerceau.
+narrateur|En ce moment, Victorina prend le cerceau.
+narrateur|Le bois du cerceau est lisse, un peu froid.
+enfant-f|Je veux le faire rouler jusqu'au mur.
+narrateur|Elle pousse le cerceau entre les feuilles.
+narrateur|Il roule, puis s'arrête près d'une flaque.
+enfant-f|Encore.
+narrateur|Une feuille colle au bois.
 narrateur|Elle la retire, tout doux.
+narrateur|Le cerceau repart, plus loin.
 narrateur|Chouchou arrive très vite.
-narrateur|Chouchou passe trop près.
+narrateur|Chouchou passe trop près du cerceau.
+narrateur|Le cerceau penche, puis tombe.
 narrateur|Victorina sent ses pieds bouger.
 narrateur|Son cœur tape.
 enfant-f|Stop.
-narrateur|Victorina fait un pas.
-narrateur|Elle peut s'éloigner.
-narrateur|S'éloigner, c'est aller vers la maîtresse.
-narrateur|Victorina marche vers le préau.
+narrateur|Sa voix est claire.
+narrateur|Elle fait un pas vers le préau.
+narrateur|Ses chaussures froissent les feuilles.
+narrateur|Elle marche jusqu'à la maîtresse.
 enfant-f|Chouchou est passé trop près.
 narrateur|La maîtresse l'écoute.
 narrateur|Victorina reste près d'elle.
-narrateur|Plus tard, près des plots oranges, Chouchou arrive encore.
-narrateur|Il passe trop près encore.
-narrateur|Victorina se souvient.
+narrateur|Elle pose une main sur le pilier.
+narrateur|Le pilier est froid et un peu rugueux.
+enfant-f|Je reste ici.
+narrateur|Le cerceau attend dans les feuilles.
+narrateur|Victorina souffle.
+narrateur|Son cœur tape moins vite.
+narrateur|Plus tard, le soleil a bougé.
+narrateur|Les plots oranges sont chauds au milieu.
+narrateur|Victorina reprend le cerceau.
+enfant-f|Je veux passer entre les plots.
+narrateur|Le cerceau roule vers l'orange.
+narrateur|Il frappe un plot, tout doux.
+narrateur|Le plot tremble, puis tient.
+enfant-f|Encore.
+narrateur|Chouchou arrive encore, très vite.
+narrateur|Il passe trop près des plots.
+narrateur|Le cerceau tombe contre un plot.
+narrateur|Le plastique fait un petit bruit creux.
+narrateur|Victorina sent encore son cœur.
 enfant-f|Stop.
-narrateur|Elle s'éloigne.
-narrateur|Elle va vers la maîtresse.
-enfant-f|Je suis venue.
+narrateur|Elle fait un pas.
+narrateur|La maîtresse est près du portail, maintenant.
+narrateur|Victorina marche vers elle.
+narrateur|L'orange des plots reste derrière.
+enfant-f|Encore trop près.
 narrateur|La maîtresse l'écoute encore.
 narrateur|Victorina reste près d'elle.
-narrateur|Elle pose une main sur un plot orange.
-narrateur|Le plot est lisse et un peu tiède.
+narrateur|Elle touche un plot, au passage.
+narrateur|Le plot est lisse et tiède.
 enfant-f|Je reste ici.
-narrateur|Victorina souffle.
-narrateur|Son cœur tape moins vite.
+narrateur|Elle souffle.
+narrateur|Le cerceau ne roule plus.
 narrateur|Le soir, papa revient.
 narrateur|Les feuilles collent encore aux chaussures.
 narrateur|Victorina secoue une feuille du talon.
 narrateur|La feuille tombe, toute plate.
-papa|Tu as joué au cerceau ?
-enfant-f|Oui.
+papa|Tu as senti le pain, encore ?
+enfant-f|Un peu.
+enfant-f|Le cerceau a roulé.
 enfant-f|Chouchou est passé trop près.
-enfant-f|Deux fois.
 enfant-f|J'ai dit stop.
 enfant-f|Je suis allée vers la maîtresse.
+papa|Près du préau ?
+enfant-f|Oui.
+papa|Et près des plots ?
+enfant-f|Stop encore.
 papa|Bravo, Victorina.
-papa|Tu as dit stop.
-papa|Tu t'es éloignée.
-papa|Tu es allée vers la maîtresse.
-papa|Même près des plots ?
-enfant-f|Oui.
-enfant-f|Stop encore.
-papa|Même leçon, autre endroit.
+papa|Tu es allée près d'elle.
 enfant-f|Oui, papa.
 narrateur|Victorina serre la main de papa.
-narrateur|Le pain du fournil sent encore, tout doux.</t>
+narrateur|La bouffée de pain revient, tout doux.</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1473,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Elle dit stop, puis elle va vers la maîtresse. Que fait Hortense ?</t>
+          <t>Elle dit stop, puis elle va vers la maîtresse. Que fait Victorina ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1494,14 +1515,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA3" s="2" t="n">
         <v>0.9</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1601,12 +1622,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Victorina a dit stop. Elle s'est éloignée. Elle a rejoint la maîtresse. Bravo. Tu as su deux fois. Stop, puis la maîtresse. Oui.</t>
+          <t>Victorina a dit stop. Elle a fait un pas. Elle a rejoint la maîtresse. Bravo. Près du préau, et près des plots. Stop, puis la maîtresse. Oui.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Victorina a dit stop. Elle s'est éloignée. Elle a rejoint la maîtresse. Bravo. Tu as su deux fois. Stop, puis la maîtresse. Oui.</t>
+          <t>Victorina a dit stop. Elle a fait un pas. Elle a rejoint la maîtresse. Bravo. Près du préau, et près des plots. Stop, puis la maîtresse. Oui.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1669,7 +1690,7 @@
         <v>0.96</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1746,10 +1767,10 @@
       <c r="AW4" t="inlineStr">
         <is>
           <t>narrateur|Victorina a dit stop.
-narrateur|Elle s'est éloignée.
+narrateur|Elle a fait un pas.
 narrateur|Elle a rejoint la maîtresse.
 papa|Bravo.
-papa|Tu as su deux fois.
+papa|Près du préau, et près des plots.
 enfant-f|Stop, puis la maîtresse.
 papa|Oui.</t>
         </is>
@@ -1778,12 +1799,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Victorina range son manteau. Une feuille mouillée reste sous la chaussure. On marche à côté ? Oui, papa. Tu tiens ma main ? Oui. Tu sens encore le pain ? Un peu. Les plots oranges restent dans la cour. Le cerceau ne roule plus. On sent encore le fournil ? Un tout petit peu. Une feuille sèche sur le chemin.</t>
+          <t>Victorina range son manteau. Une feuille mouillée reste sous la chaussure. On marche à côté ? Oui, papa. Tu tiens ma main ? Oui. Tu sens encore le pain ? Un tout petit peu. Les plots oranges restent dans la cour. Le cerceau ne roule plus. On laisse le cerceau près du mur ? Oui. Une feuille sèche sur le chemin.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Victorina range son manteau. Une feuille mouillée reste sous la chaussure. On marche à côté ? Oui, papa. Tu tiens ma main ? Oui. Tu sens encore le pain ? Un peu. Les plots oranges restent dans la cour. Le cerceau ne roule plus. On sent encore le fournil ? Un tout petit peu. Une feuille sèche sur le chemin.</t>
+          <t>Victorina range son manteau. Une feuille mouillée reste sous la chaussure. On marche à côté ? Oui, papa. Tu tiens ma main ? Oui. Tu sens encore le pain ? Un tout petit peu. Les plots oranges restent dans la cour. Le cerceau ne roule plus. On laisse le cerceau près du mur ? Oui. Une feuille sèche sur le chemin.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1846,7 +1867,7 @@
         <v>0.96</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1921,11 +1942,11 @@
 papa|Tu tiens ma main ?
 enfant-f|Oui.
 papa|Tu sens encore le pain ?
-enfant-f|Un peu.
+enfant-f|Un tout petit peu.
 narrateur|Les plots oranges restent dans la cour.
 narrateur|Le cerceau ne roule plus.
-papa|On sent encore le fournil ?
-enfant-f|Un tout petit peu.
+papa|On laisse le cerceau près du mur ?
+enfant-f|Oui.
 narrateur|Une feuille sèche sur le chemin.</t>
         </is>
       </c>
@@ -1953,12 +1974,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai dit stop. Je suis allée vers la maîtresse. Bravo, Victorina. Les feuilles mouillées restent au sol.</t>
+          <t>J'ai dit stop. Je suis allée vers la maîtresse. Bravo, Victorina. Les feuilles jaunes restent au sol, toutes plates.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>J'ai dit stop. Je suis allée vers la maîtresse. Bravo, Victorina. Les feuilles mouillées restent au sol.</t>
+          <t>J'ai dit stop. Je suis allée vers la maîtresse. Bravo, Victorina. Les feuilles jaunes restent au sol, toutes plates.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2021,7 +2042,7 @@
         <v>0.92</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2096,7 +2117,7 @@
           <t>enfant-f|J'ai dit stop.
 enfant-f|Je suis allée vers la maîtresse.
 papa|Bravo, Victorina.
-narrateur|Les feuilles mouillées restent au sol.</t>
+narrateur|Les feuilles jaunes restent au sol, toutes plates.</t>
         </is>
       </c>
     </row>
@@ -2117,7 +2138,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2167,6 +2188,13 @@
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
